--- a/examples/Task2/synthetic/payment_registry_synthetic.xlsx
+++ b/examples/Task2/synthetic/payment_registry_synthetic.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Export" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46058</v>
+        <v>46054</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>46037</v>
+        <v>46028</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>250 000</t>
+          <t>1 003 300</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -590,24 +590,24 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46086</v>
+        <v>46054</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ООО «Недвижимость Плюс»</t>
+          <t>АО «Бизнес-Парк Северный»</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DOG-ARND-01</t>
+          <t>DOG-ARND-02</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>250 000</t>
+          <t>632 100</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -630,24 +630,24 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46117</v>
+        <v>46086</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ООО «Недвижимость Плюс»</t>
+          <t>АО «Бизнес-Парк Северный»</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DOG-ARND-01</t>
+          <t>DOG-ARND-02</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>250 000,50</t>
+          <t>629 300</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -670,24 +670,24 @@
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46068</v>
+        <v>46054</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>АО «Авиакомпания Лидер»</t>
+          <t>ООО «Городские Площади»</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DOG-AVIA-02</t>
+          <t>DOG-ARND-03</t>
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>46054</v>
+        <v>46030</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1 200 000</t>
+          <t>821 500</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -710,24 +710,24 @@
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46096</v>
+        <v>46086</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>АО «Авиакомпания Лидер»</t>
+          <t>ООО «Городские Площади»</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DOG-AVIA-02</t>
+          <t>DOG-ARND-03</t>
         </is>
       </c>
       <c r="I8" s="1" t="n">
-        <v>46054</v>
+        <v>46030</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>800 000</t>
+          <t>738 400</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -750,24 +750,24 @@
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46091</v>
+        <v>46054</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>АО СК «Надёжный Полис»</t>
+          <t>ЗАО «Офис Инвест»</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DOG-INS-03</t>
+          <t>DOG-ARND-04</t>
         </is>
       </c>
       <c r="I9" s="1" t="n">
-        <v>46082</v>
+        <v>46031</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>850 000</t>
+          <t>1 827 400</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -790,24 +790,24 @@
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>АНО ДПО «Учебный Центр»</t>
+          <t>ООО «АльфаРент»</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DOG-EDU-04</t>
+          <t>DOG-ARND-05</t>
         </is>
       </c>
       <c r="I10" s="1" t="n">
-        <v>46073</v>
+        <v>46032</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>175 000</t>
+          <t>637 500</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -830,24 +830,24 @@
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46113</v>
+        <v>46086</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>АНО ДПО «Учебный Центр»</t>
+          <t>ООО «АльфаРент»</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DOG-EDU-04</t>
+          <t>DOG-ARND-05</t>
         </is>
       </c>
       <c r="I11" s="1" t="n">
-        <v>46073</v>
+        <v>46032</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>175 000</t>
+          <t>637 200</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46073</v>
+        <v>46122</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ПАО «Связной Оператор»</t>
+          <t>ООО «АльфаРент»</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DOG-POST-05</t>
+          <t>DOG-ARND-05</t>
         </is>
       </c>
       <c r="I12" s="1" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>45 000; 45 000</t>
+          <t>645 600</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -910,24 +910,24 @@
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46101</v>
+        <v>46082</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ПАО «Связной Оператор»</t>
+          <t>АО «Авиакомпания Лидер»</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DOG-POST-05</t>
+          <t>DOG-AVIA-01</t>
         </is>
       </c>
       <c r="I13" s="1" t="n">
-        <v>46032</v>
+        <v>46055</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>45 000</t>
+          <t>1 030 500</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -950,24 +950,24 @@
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46073</v>
+        <v>46117</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ООО «Средний Партнёр»</t>
+          <t>АО «Авиакомпания Лидер»</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DOG-SMSP-06</t>
+          <t>DOG-AVIA-01</t>
         </is>
       </c>
       <c r="I14" s="1" t="n">
-        <v>46058</v>
+        <v>46055</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3 000 000</t>
+          <t>1 066 200</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -990,24 +990,24 @@
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46101</v>
+        <v>46082</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ООО «Средний Партнёр»</t>
+          <t>ПАО «Аэрофлот»</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DOG-SMSP-06</t>
+          <t>DOG-AVIA-02</t>
         </is>
       </c>
       <c r="I15" s="1" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2 500 000</t>
+          <t>2 723 600</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1030,24 +1030,24 @@
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>46132</v>
+        <v>46082</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ООО «Средний Партнёр»</t>
+          <t>ООО «Сибирские Авиалинии»</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DOG-SMSP-06</t>
+          <t>DOG-AVIA-03</t>
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2 500 000</t>
+          <t>1 693 800</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1070,24 +1070,24 @@
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>46106</v>
+        <v>46117</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ООО «Малый Поставщик»</t>
+          <t>ООО «Сибирские Авиалинии»</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DOG-SMSP-07</t>
+          <t>DOG-AVIA-03</t>
         </is>
       </c>
       <c r="I17" s="1" t="n">
-        <v>46091</v>
+        <v>46059</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1 600 000</t>
+          <t>1 685 200</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1110,24 +1110,24 @@
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46137</v>
+        <v>46082</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ООО «Малый Поставщик»</t>
+          <t>АО «Уральские Перевозки»</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DOG-SMSP-07</t>
+          <t>DOG-AVIA-04</t>
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>46091</v>
+        <v>46061</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1 600 000</t>
+          <t>1 278 900</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1150,24 +1150,24 @@
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>46127</v>
+        <v>46117</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ИП Иванов А.А.</t>
+          <t>АО «Уральские Перевозки»</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DOG-MICRO-08</t>
+          <t>DOG-AVIA-04</t>
         </is>
       </c>
       <c r="I19" s="1" t="n">
-        <v>46113</v>
+        <v>46061</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>225 000</t>
+          <t>1 308 900</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1190,24 +1190,24 @@
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>46157</v>
+        <v>46152</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ИП Иванов А.А.</t>
+          <t>АО «Уральские Перевозки»</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DOG-MICRO-08</t>
+          <t>DOG-AVIA-04</t>
         </is>
       </c>
       <c r="I20" s="1" t="n">
-        <v>46113</v>
+        <v>46061</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>225 000</t>
+          <t>1 327 200</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1230,24 +1230,24 @@
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>46063</v>
+        <v>46113</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ООО «Общий Поставщик»</t>
+          <t>АО СК «Надёжный Полис»</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DOG-REG-09</t>
+          <t>DOG-INS-01</t>
         </is>
       </c>
       <c r="I21" s="1" t="n">
-        <v>46047</v>
+        <v>46083</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>400 000</t>
+          <t>350 900</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1270,24 +1270,24 @@
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>46091</v>
+        <v>46147</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ООО «Общий Поставщик»</t>
+          <t>АО СК «Надёжный Полис»</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DOG-REG-09</t>
+          <t>DOG-INS-01</t>
         </is>
       </c>
       <c r="I22" s="1" t="n">
-        <v>46047</v>
+        <v>46083</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>350 000</t>
+          <t>449 500</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1310,24 +1310,24 @@
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ООО «Копеечный Сервис»</t>
+          <t>ООО СК «РосГарантия»</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DOG-SMALL-10</t>
+          <t>DOG-INS-02</t>
         </is>
       </c>
       <c r="I23" s="1" t="n">
-        <v>46065</v>
+        <v>46085</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>45 000</t>
+          <t>541 500</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1350,41 +1350,36 @@
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>46042</v>
+        <v>46147</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ForeignCorp Ltd</t>
+          <t>ООО СК «РосГарантия»</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>USD-FOREIGN-01</t>
+          <t>DOG-INS-02</t>
         </is>
       </c>
       <c r="I24" s="1" t="n">
-        <v>46027</v>
+        <v>46085</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>505 400</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>480 000,00</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>RUB</t>
         </is>
       </c>
     </row>
@@ -1399,20 +1394,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ООО «Неопознанный контрагент»</t>
+          <t>АО «АльфаСтрахование»</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>UNKNOWN-XX</t>
+          <t>DOG-INS-03</t>
         </is>
       </c>
       <c r="I25" s="1" t="n">
-        <v>46096</v>
+        <v>46087</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>123 456,78</t>
+          <t>586 400</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1423,6 +1418,4691 @@
         </is>
       </c>
       <c r="AK25" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>АО «АльфаСтрахование»</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DOG-INS-03</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>570 400</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ООО «Финансовый Партнёр»</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DOG-INS-04</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>694 100</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ООО «Финансовый Партнёр»</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DOG-INS-04</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>663 400</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>АНО ДПО «Учебный Центр»</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>DOG-EDU-01</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>279 800</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ООО «Корпоративный Университет»</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DOG-EDU-02</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>357 100</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ФГБОУ ВО «Технический Институт»</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>DOG-EDU-03</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>249 100</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ФГБОУ ВО «Технический Институт»</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DOG-EDU-03</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>204 700</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ООО «Бизнес-Школа Лидер»</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DOG-EDU-04</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>565 600</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ПАО «Связной Оператор»</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DOG-POST-01</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>46032</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>77 000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ПАО «Связной Оператор»</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>DOG-POST-01</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>46032</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>23 000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ПАО «Связной Оператор»</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DOG-POST-01</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>46032</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>56 300</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>АО «МегаСвязь»</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DOG-POST-02</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>242 400</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ФГУП «Почта России»</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DOG-POST-03</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>167 400</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ФГУП «Почта России»</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DOG-POST-03</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>166 100</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ООО «Логистик Экспресс»</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DOG-POST-04</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>185 700</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ООО «Логистик Экспресс»</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DOG-POST-04</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>135 200</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ООО «Средний Партнёр»</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-01</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6 456 000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>АО «Среднеотраслевые Решения»</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-02</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3 987 900</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>АО «Среднеотраслевые Решения»</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-02</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3 960 500</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ООО «БетаПром»</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-03</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4 713 200</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ООО «БетаПром»</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-03</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4 749 800</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>АО «ГаммаЛогистик»</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-04</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>5 509 400</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>АО «ГаммаЛогистик»</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-04</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>5 533 300</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ООО «Дельта-Консалтинг»</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-05</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>6 221 300</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ООО «Дельта-Консалтинг»</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MED-05</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>6 248 500</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ООО «Малый Поставщик»</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1 277 500</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ООО «Малый Поставщик»</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1 337 800</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ООО «Эпсилон-Сервис»</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-02</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1 642 000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ООО «Эпсилон-Сервис»</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-02</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1 639 600</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ООО «Зета-Сетевик»</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-03</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3 829 800</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ООО «Эта-Решения»</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-04</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2 220 000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ООО «Эта-Решения»</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-04</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2 245 600</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ООО «Тета-Партнёр»</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-05</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2 471 400</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ООО «Тета-Партнёр»</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-05</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2 510 600</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ООО «Йота-Логистика»</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-06</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1 852 000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ООО «Йота-Логистика»</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-06</t>
+        </is>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1 900 600</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ООО «Йота-Логистика»</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-06</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1 906 900</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ИП Иванов А.А.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-01</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>264 700</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ИП Иванов А.А.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-01</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>217 500</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ИП Смирнов В.К.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-02</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>530 000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ООО «Каппа-Сервис»</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-03</t>
+        </is>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>641 300</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ИП Кузнецов Д.С.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-04</t>
+        </is>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>235 100</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ИП Кузнецов Д.С.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-04</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>208 700</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ИП Кузнецов Д.С.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-04</t>
+        </is>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>227 700</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ООО «Лямбда-Микро»</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-05</t>
+        </is>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>402 900</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ООО «Лямбда-Микро»</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-05</t>
+        </is>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>460 900</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ООО «Сигма-Технология»</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>335 200</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ООО «Сигма-Технология»</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>367 600</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ООО «Сигма-Технология»</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>343 500</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ООО «Тау-Сервис»</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-02</t>
+        </is>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>584 700</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ООО «Тау-Сервис»</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-02</t>
+        </is>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>568 300</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ООО «Ипсилон-Поставка»</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-03</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>747 600</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ООО «Ипсилон-Поставка»</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-03</t>
+        </is>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>723 600</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ООО «Фи-Логистик»</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-04</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>46124</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>847 900</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ООО «Фи-Логистик»</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-04</t>
+        </is>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>46124</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>826 600</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ООО «Хи-Решения»</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-05</t>
+        </is>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>626 500</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ООО «Хи-Решения»</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-05</t>
+        </is>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>602 400</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ООО «Хи-Решения»</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>DOG-WITH-SMALL-05</t>
+        </is>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>597 400</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ИП Петров И.С.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-01</t>
+        </is>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>133 100</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ИП Петров И.С.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-01</t>
+        </is>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>181 800</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ИП Орлов М.В.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-02</t>
+        </is>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>98 600</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ИП Орлов М.В.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-02</t>
+        </is>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>185 700</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ИП Орлов М.В.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-02</t>
+        </is>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>92 800</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ООО «Пси-Микропоставка»</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-03</t>
+        </is>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>460 000</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ИП Соколов А.Н.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-04</t>
+        </is>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>324 200</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ИП Соколов А.Н.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-04</t>
+        </is>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>290 300</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ИП Васильев Е.П.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>DOG-WITH-MICRO-05</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>650 400</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ООО «Общий Поставщик»</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>DOG-REG-01</t>
+        </is>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>278 100</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ООО «Общий Поставщик»</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>DOG-REG-01</t>
+        </is>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>261 300</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ООО «Общий Поставщик»</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>DOG-REG-01</t>
+        </is>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>269 400</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>АО «Стандарт-Сервис»</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>DOG-REG-02</t>
+        </is>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>522 500</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>АО «Стандарт-Сервис»</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DOG-REG-02</t>
+        </is>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>451 500</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ООО «РосТехОборудование»</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>DOG-REG-03</t>
+        </is>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1 289 400</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>АО «ИндустриалПром»</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>DOG-REG-04</t>
+        </is>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>46040</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>784 000</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>АО «ИндустриалПром»</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>DOG-REG-04</t>
+        </is>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>46040</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>744 600</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ООО «МегаСнаб»</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>DOG-REG-05</t>
+        </is>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1 738 500</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>АО «Универсал-Логистик»</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>DOG-REG-06</t>
+        </is>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>637 400</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>АО «Универсал-Логистик»</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>DOG-REG-06</t>
+        </is>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>676 100</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>АО «Универсал-Логистик»</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>DOG-REG-06</t>
+        </is>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>617 100</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ООО «Промторг»</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>DOG-REG-07</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>46046</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1 140 600</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ООО «Промторг»</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>DOG-REG-07</t>
+        </is>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>46046</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1 174 900</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>АО «БизнесЛидер»</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>DOG-REG-08</t>
+        </is>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1 266 500</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>АО «БизнесЛидер»</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>DOG-REG-08</t>
+        </is>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>1 213 900</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ООО «Копеечный Сервис»</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>DOG-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>56 200</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ООО «Копеечный Сервис»</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>DOG-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>39 000</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ИП Михайлов В.С.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>DOG-SMALL-02</t>
+        </is>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>1 000</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ИП Михайлов В.С.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>DOG-SMALL-02</t>
+        </is>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>29 000</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ООО «Малая Поставка»</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>DOG-SMALL-03</t>
+        </is>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>58 200</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ООО «Малая Поставка»</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>DOG-SMALL-03</t>
+        </is>
+      </c>
+      <c r="I114" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>ИП Захаров А.Ю.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>DOG-SMALL-04</t>
+        </is>
+      </c>
+      <c r="I115" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>118 500</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ООО «Длящийся Сервис»</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>DOG-CONT-01</t>
+        </is>
+      </c>
+      <c r="I116" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>289 000</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ООО «Длящийся Сервис»</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>DOG-CONT-01</t>
+        </is>
+      </c>
+      <c r="I117" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>227 600</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>АО «Многолетние Поставки»</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>DOG-CONT-02</t>
+        </is>
+      </c>
+      <c r="I118" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>697 600</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ООО «Долгосрочный Партнёр»</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>DOG-CONT-03</t>
+        </is>
+      </c>
+      <c r="I119" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>406 400</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ООО «Долгосрочный Партнёр»</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>DOG-CONT-03</t>
+        </is>
+      </c>
+      <c r="I120" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>382 600</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ForeignCorp Ltd</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-01</t>
+        </is>
+      </c>
+      <c r="I121" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>274 400</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>20 000 000</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ForeignCorp Ltd</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-01</t>
+        </is>
+      </c>
+      <c r="I122" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>210 300</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>20 000 000</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>EuroSupply GmbH</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-02</t>
+        </is>
+      </c>
+      <c r="I123" s="1" t="n">
+        <v>46032</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>745 900</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>63 000 000</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Asia Trading Co.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-03</t>
+        </is>
+      </c>
+      <c r="I124" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>259 100</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>24 000 000</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Asia Trading Co.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-03</t>
+        </is>
+      </c>
+      <c r="I125" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>349 700</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>24 000 000</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Asia Trading Co.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-03</t>
+        </is>
+      </c>
+      <c r="I126" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>319 800</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>24 000 000</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>46096</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ПАО «Связной Оператор»</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>DOG-POST-01</t>
+        </is>
+      </c>
+      <c r="I127" s="1" t="n">
+        <v>46032</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>45 000; 35 000</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ООО «Общий Поставщик»</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>DOG-REG-01</t>
+        </is>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>125 000; 75 000; 50 000</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ООО «Малый Поставщик»</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-SMALL-01</t>
+        </is>
+      </c>
+      <c r="I129" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>200 000; 200 000</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>ИП Иванов А.А.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>DOG-SMSP-MICRO-01</t>
+        </is>
+      </c>
+      <c r="I130" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>120 000; 80 000</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>ForeignCorp Ltd</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-01</t>
+        </is>
+      </c>
+      <c r="I131" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>400 000,00</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>EuroSupply GmbH</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-02</t>
+        </is>
+      </c>
+      <c r="I132" s="1" t="n">
+        <v>46032</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>765 000,00</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Asia Trading Co.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>DOG-FRGN-03</t>
+        </is>
+      </c>
+      <c r="I133" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>3 200</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>256 000,00</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ООО «Неопознанный Поставщик»</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>UNKNOWN-001</t>
+        </is>
+      </c>
+      <c r="I134" s="1" t="n">
+        <v>46096</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>123 456</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ИП Незаключённый</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>ORPHAN-002</t>
+        </is>
+      </c>
+      <c r="I135" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>85 000</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ООО «Неизвестный Контрагент»</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>MISSING-003</t>
+        </is>
+      </c>
+      <c r="I136" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>450 000</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ИП Иванов Бесконтрактный</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>NOREG-004</t>
+        </is>
+      </c>
+      <c r="I137" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>67 300</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ООО «Внешний Поставщик»</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>EXTERNAL-005</t>
+        </is>
+      </c>
+      <c r="I138" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>312 500,00</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ООО «Длящийся Сервис»</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>DOG-CONT-01</t>
+        </is>
+      </c>
+      <c r="I139" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>150 000</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>АО «Многолетние Поставки»</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>DOG-CONT-02</t>
+        </is>
+      </c>
+      <c r="I140" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>200 000</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Платеж</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ООО «Долгосрочный Партнёр»</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>DOG-CONT-03</t>
+        </is>
+      </c>
+      <c r="I141" s="1" t="n">
+        <v>45976</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>300 000</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
